--- a/tools/xlsform_samples/WEMWBS.xlsx
+++ b/tools/xlsform_samples/WEMWBS.xlsx
@@ -442,11 +442,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -1000,84 +1000,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WEMWBS_scoring</t>
+          <t>WEMWBS_wemwbs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>wemwbs (sum_coded)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>${wemwbs1} + ${wemwbs2} + ${wemwbs3} + ${wemwbs4} + ${wemwbs5} + ${wemwbs6} + ${wemwbs7} + ${wemwbs8} + ${wemwbs9} + ${wemwbs10} + ${wemwbs11} + ${wemwbs12} + ${wemwbs13} + ${wemwbs14}</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WEMWBS_wemwbs</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>wemwbs (sum_coded)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>${wemwbs1} + ${wemwbs2} + ${wemwbs3} + ${wemwbs4} + ${wemwbs5} + ${wemwbs6} + ${wemwbs7} + ${wemwbs8} + ${wemwbs9} + ${wemwbs10} + ${wemwbs11} + ${wemwbs12} + ${wemwbs13} + ${wemwbs14}</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>WEMWBS_scoring</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/WEMWBS.xlsx
+++ b/tools/xlsform_samples/WEMWBS.xlsx
@@ -1206,7 +1206,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
